--- a/SA2502049_Automation_Project/CreateLoginDataFile.xlsx
+++ b/SA2502049_Automation_Project/CreateLoginDataFile.xlsx
@@ -12,15 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>UserName</t>
   </si>
   <si>
     <t>Password</t>
-  </si>
-  <si>
-    <t>Flag</t>
   </si>
   <si>
     <t>Deepak</t>
@@ -29,16 +26,10 @@
     <t>Paratkar</t>
   </si>
   <si>
-    <t>true</t>
-  </si>
-  <si>
     <t>Pratik</t>
   </si>
   <si>
     <t>Patni</t>
-  </si>
-  <si>
-    <t>false</t>
   </si>
   <si>
     <t>Soumya</t>
@@ -51,9 +42,6 @@
   </si>
   <si>
     <t>Yadav</t>
-  </si>
-  <si>
-    <t>False</t>
   </si>
   <si>
     <t>John</t>
@@ -114,63 +102,63 @@
       <c r="B1" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="0">
-        <v>2</v>
+      <c r="C1" t="n" s="0">
+        <v>0.0</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>5</v>
+      <c r="C2" t="n" s="0">
+        <v>1.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>7</v>
+        <v>5</v>
       </c>
-      <c r="C3" t="s" s="0">
-        <v>8</v>
+      <c r="C3" t="n" s="0">
+        <v>1.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
-      <c r="C4" t="s" s="0">
-        <v>5</v>
+      <c r="C4" t="n" s="0">
+        <v>1.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>12</v>
+        <v>9</v>
       </c>
-      <c r="C5" t="s" s="0">
-        <v>13</v>
+      <c r="C5" t="n" s="0">
+        <v>0.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>15</v>
+        <v>11</v>
       </c>
-      <c r="C6" t="s" s="0">
-        <v>5</v>
+      <c r="C6" t="n" s="0">
+        <v>1.0</v>
       </c>
     </row>
   </sheetData>
